--- a/currentbuild/StructureDefinition-auditevent-practitioner.xlsx
+++ b/currentbuild/StructureDefinition-auditevent-practitioner.xlsx
@@ -24,13 +24,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>urn:no-basis-auditevent/StructureDefinition/auditevent-practitioner</t>
+    <t>http://hl7.no/fhir/StructureDefinition/auditevent-practitioner</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-28T16:36:28+00:00</t>
+    <t>2024-06-04T05:44:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -105,7 +105,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>urn:no-basis-auditevent/StructureDefinition/NoBasisPractitioner</t>
+    <t>http://hl7.no/fhir/StructureDefinition/no-basis-Practitioner</t>
   </si>
   <si>
     <t>Abstract</t>

--- a/currentbuild/StructureDefinition-auditevent-practitioner.xlsx
+++ b/currentbuild/StructureDefinition-auditevent-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T05:44:14+00:00</t>
+    <t>2024-06-04T06:11:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/currentbuild/StructureDefinition-auditevent-practitioner.xlsx
+++ b/currentbuild/StructureDefinition-auditevent-practitioner.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2238" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3508" uniqueCount="495">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T06:11:20+00:00</t>
+    <t>2024-06-06T18:49:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -469,10 +469,18 @@
     <t>practitioner:identifier and practitioner:hpr-nr</t>
   </si>
   <si>
-    <t>An identifier that applies to this person in this role.</t>
+    <t>An identifier that applies to this person in this role.
+In Norway all registered health care personnel is registered in the Helsepersonellregister (HPR) and is assigned a HPR-number that is used to identify the health care practitioner. Health care personnel not registered in HPR can use FNR for identification.</t>
   </si>
   <si>
     <t>Often, specific identities are assigned for the agent.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
+    <t>open</t>
   </si>
   <si>
     <t>PRD-7 (or XCN.1)</t>
@@ -517,9 +525,6 @@
   </si>
   <si>
     <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
   </si>
   <si>
     <t>Element.extension</t>
@@ -782,6 +787,148 @@
     <t>Reference.display</t>
   </si>
   <si>
+    <t>Practitioner.identifier:HPR</t>
+  </si>
+  <si>
+    <t>HPR</t>
+  </si>
+  <si>
+    <t>HPR number</t>
+  </si>
+  <si>
+    <t>In Norway all registered health care personnel is registered in the Helsepersonellregister (HPR) and is assigned a HPR-number that is used to identify the health care practitioner. Health care personnel not registered in HPR can use FNR for identification.
+The norwegian helsepersonellnummer for the practitioner. HPR as one of the possible practitioner identification numbers, should at least be sent unless there is a reason not to. Reasons for not sending the HPR number include but are not limited to, research and apps without a contract for processing data.</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:HPR.id</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:HPR.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:HPR.use</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:HPR.type</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:HPR.system</t>
+  </si>
+  <si>
+    <t>The identifier for HPR number</t>
+  </si>
+  <si>
+    <t>urn:oid:2.16.578.1.12.4.1.4.4</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:HPR.value</t>
+  </si>
+  <si>
+    <t>The acttual HPR-number</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:HPR.period</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:HPR.assigner</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:FNR</t>
+  </si>
+  <si>
+    <t>FNR</t>
+  </si>
+  <si>
+    <t>Norwegian FNR</t>
+  </si>
+  <si>
+    <t>Fødselsnummer for the practitioner. Fødselsnummer as one of the possible practitioner identification numbers. Reasons for not sending the Fødselsnummer include but are not limited to, research and apps without a contract for processing data.</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:FNR.id</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:FNR.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:FNR.use</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:FNR.type</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:FNR.system</t>
+  </si>
+  <si>
+    <t>The identification of FNR</t>
+  </si>
+  <si>
+    <t>urn:oid:2.16.578.1.12.4.1.4.1</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:FNR.value</t>
+  </si>
+  <si>
+    <t>The actual FNR</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:FNR.period</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:FNR.assigner</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:DNR</t>
+  </si>
+  <si>
+    <t>DNR</t>
+  </si>
+  <si>
+    <t>The D-nummer of the practitioner</t>
+  </si>
+  <si>
+    <t>The D-nummer of the practitioner. (assigned by the norwegian Skatteetaten)</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:DNR.id</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:DNR.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:DNR.use</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:DNR.type</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:DNR.system</t>
+  </si>
+  <si>
+    <t>The identification of the D-nummer</t>
+  </si>
+  <si>
+    <t>The identification of the Norwegian D-nummer</t>
+  </si>
+  <si>
+    <t>urn:oid:2.16.578.1.12.4.1.4.2</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:DNR.value</t>
+  </si>
+  <si>
+    <t>The actual D-nummer</t>
+  </si>
+  <si>
+    <t>The actual Norwegian D-nummer</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:DNR.period</t>
+  </si>
+  <si>
+    <t>Practitioner.identifier:DNR.assigner</t>
+  </si>
+  <si>
     <t>Practitioner.active</t>
   </si>
   <si>
@@ -813,216 +960,33 @@
     <t>Practitioner.name</t>
   </si>
   <si>
-    <t xml:space="preserve">HumanName
+    <t xml:space="preserve">HumanName {http://hl7.no/fhir/StructureDefinition/no-basis-HumanName}
 </t>
   </si>
   <si>
-    <t>The name(s) associated with the practitioner</t>
-  </si>
-  <si>
-    <t>The name(s) associated with the practitioner.</t>
-  </si>
-  <si>
-    <t>The selection of the use property should ensure that there is a single usual name specified, and others use the nickname (alias), old, or other values as appropriate.  --In general, select the value to be used in the ResourceReference.display based on this:--1. There is more than 1 name-2. Use = usual-3. Period is current to the date of the usage-4. Use = official-5. Other order as decided by internal business rules.</t>
+    <t>Norwegian human name</t>
+  </si>
+  <si>
+    <t>Defines the format of norwegian human name according to norwegian legislation (lov om personnavn).</t>
+  </si>
+  <si>
+    <t>Names may be changed, or repudiated, or people may have different names in different contexts. Names may be divided into parts of different type that have variable significance depending on context, though the division into parts does not always matter. With personal names, the different parts might or might not be imbued with some implicit meaning; various cultures associate different importance with the name parts and the degree to which systems must care about name parts around the world varies widely.</t>
   </si>
   <si>
     <t>The name(s) that a Practitioner is known by. Where there are multiple, the name that the practitioner is usually known as should be used in the display.</t>
   </si>
   <si>
-    <t>XCN Components</t>
-  </si>
-  <si>
-    <t>./name</t>
-  </si>
-  <si>
-    <t>./PreferredName (GivenNames, FamilyName, TitleCode)</t>
-  </si>
-  <si>
-    <t>Practitioner.name.id</t>
-  </si>
-  <si>
-    <t>Practitioner.name.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.name.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | nickname | anonymous | old | maiden</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this name.</t>
-  </si>
-  <si>
-    <t>Applications can assume that a name is current unless it explicitly says that it is temporary or old.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
-  </si>
-  <si>
-    <t>The use of a human name.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/name-use|4.0.1</t>
-  </si>
-  <si>
-    <t>HumanName.use</t>
-  </si>
-  <si>
-    <t>XPN.7, but often indicated by which field contains the name</t>
-  </si>
-  <si>
-    <t>unique(./use)</t>
-  </si>
-  <si>
-    <t>./NamePurpose</t>
-  </si>
-  <si>
-    <t>Practitioner.name.text</t>
-  </si>
-  <si>
-    <t>practitioner:identifier:name</t>
-  </si>
-  <si>
-    <t>Specifies the entire name as it should be displayed e.g. on an application UI. This may be provided instead of or as well as the specific parts.</t>
-  </si>
-  <si>
-    <t>Can provide both a text representation and parts. Applications updating a name SHALL ensure that when both text and parts are present,  no content is included in the text that isn't found in a part.</t>
-  </si>
-  <si>
-    <t>A renderable, unencoded form.</t>
-  </si>
-  <si>
-    <t>HumanName.text</t>
-  </si>
-  <si>
-    <t>implied by XPN.11</t>
-  </si>
-  <si>
-    <t>./formatted</t>
-  </si>
-  <si>
-    <t>Practitioner.name.family</t>
-  </si>
-  <si>
-    <t xml:space="preserve">surname
+    <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t>Family name (often called 'Surname')</t>
-  </si>
-  <si>
-    <t>The part of a name that links to the genealogy. In some cultures (e.g. Eritrea) the family name of a son is the first name of his father.</t>
-  </si>
-  <si>
-    <t>Family Name may be decomposed into specific parts using extensions (de, nl, es related cultures).</t>
-  </si>
-  <si>
-    <t>HumanName.family</t>
-  </si>
-  <si>
-    <t>XPN.1/FN.1</t>
-  </si>
-  <si>
-    <t>./part[partType = FAM]</t>
-  </si>
-  <si>
-    <t>./FamilyName</t>
-  </si>
-  <si>
-    <t>Practitioner.name.given</t>
-  </si>
-  <si>
-    <t>first name
-middle name</t>
-  </si>
-  <si>
-    <t>Given names (not always 'first'). Includes middle names</t>
-  </si>
-  <si>
-    <t>Given name.</t>
-  </si>
-  <si>
-    <t>If only initials are recorded, they may be used in place of the full name parts. Initials may be separated into multiple given names but often aren't due to paractical limitations.  This element is not called "first name" since given names do not always come first.</t>
-  </si>
-  <si>
-    <t>HumanName.given</t>
-  </si>
-  <si>
-    <t>XPN.2 + XPN.3</t>
-  </si>
-  <si>
-    <t>./part[partType = GIV]</t>
-  </si>
-  <si>
-    <t>./GivenNames</t>
-  </si>
-  <si>
-    <t>Practitioner.name.prefix</t>
-  </si>
-  <si>
-    <t>Parts that come before the name</t>
-  </si>
-  <si>
-    <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the start of the name.</t>
-  </si>
-  <si>
-    <t>HumanName.prefix</t>
-  </si>
-  <si>
-    <t>XPN.5</t>
-  </si>
-  <si>
-    <t>./part[partType = PFX]</t>
-  </si>
-  <si>
-    <t>./TitleCode</t>
-  </si>
-  <si>
-    <t>Practitioner.name.suffix</t>
-  </si>
-  <si>
-    <t>Parts that come after the name</t>
-  </si>
-  <si>
-    <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the end of the name.</t>
-  </si>
-  <si>
-    <t>HumanName.suffix</t>
-  </si>
-  <si>
-    <t>XPN/4</t>
-  </si>
-  <si>
-    <t>./part[partType = SFX]</t>
-  </si>
-  <si>
-    <t>Practitioner.name.period</t>
-  </si>
-  <si>
-    <t>Time period when name was/is in use</t>
-  </si>
-  <si>
-    <t>Indicates the period of time when this name was valid for the named person.</t>
-  </si>
-  <si>
-    <t>Allows names to be placed in historical context.</t>
-  </si>
-  <si>
-    <t>HumanName.period</t>
-  </si>
-  <si>
-    <t>XPN.13 + XPN.14</t>
-  </si>
-  <si>
-    <t>./usablePeriod[type="IVL&lt;TS&gt;"]</t>
+    <t>XPN</t>
+  </si>
+  <si>
+    <t>EN (actually, PN)</t>
+  </si>
+  <si>
+    <t>ProviderName</t>
   </si>
   <si>
     <t>Practitioner.telecom</t>
@@ -1056,30 +1020,31 @@
     <t>Practitioner.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address
+    <t xml:space="preserve">Address {http://hl7.no/fhir/StructureDefinition/no-basis-Address}
 </t>
   </si>
   <si>
-    <t>Address(es) of the practitioner that are not role specific (typically home address)</t>
-  </si>
-  <si>
-    <t>Address(es) of the practitioner that are not role specific (typically home address). +    <t>Norwegian address</t>
+  </si>
+  <si>
+    <t>http://hl7.no/fhir/StructureDefinition/no-basis-Address
+Address(es) of the practitioner that are not role specific (typically home address).  Work addresses are not typically entered in this property as they are usually role dependent.</t>
   </si>
   <si>
-    <t>The PractitionerRole does not have an address value on it, as it is expected that the location property be used for this purpose (which has an address).</t>
+    <t>Note: address is intended to describe postal addresses for administrative purposes, not to describe absolute geographical coordinates.  Postal addresses are often used as proxies for physical locations (also see the [Location](location.html#) resource).</t>
   </si>
   <si>
     <t>The home/mailing address of the practitioner is often required for employee administration purposes, and also for some rostering services where the start point (practitioners home) can be used in calculations.</t>
   </si>
   <si>
-    <t>ORC-24, STF-11, ROL-11, PRT-14</t>
-  </si>
-  <si>
-    <t>./addr</t>
-  </si>
-  <si>
-    <t>./Addresses</t>
+    <t>XAD</t>
+  </si>
+  <si>
+    <t>AD</t>
+  </si>
+  <si>
+    <t>Address</t>
   </si>
   <si>
     <t>Practitioner.gender</t>
@@ -1166,7 +1131,7 @@
     <t>Certification, licenses, or training pertaining to the provision of care</t>
   </si>
   <si>
-    <t>The official certifications, training, and licenses that authorize or otherwise pertain to the provision of care by the practitioner.  For example, a medical license issued by a medical board authorizing the practitioner to practice medicine within a certian locality.</t>
+    <t>Coded representation of the qualification of the health care practitioner. Usually contains healthPersonnellCategory according to Kategori helsepersonell (OID=9060) and approvalType according to Godkjenningstype HPR (OID=7704)</t>
   </si>
   <si>
     <t>CER?</t>
@@ -1222,9 +1187,6 @@
     <t>Coded representation of the qualification</t>
   </si>
   <si>
-    <t>Coded representation of the qualification.</t>
-  </si>
-  <si>
     <t>example</t>
   </si>
   <si>
@@ -1250,12 +1212,6 @@
 </t>
   </si>
   <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
     <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
   </si>
   <si>
@@ -1271,121 +1227,241 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
+    <t>Practitioner.qualification.code.coding:healthPersonnellCategory</t>
+  </si>
+  <si>
+    <t>healthPersonnellCategory</t>
+  </si>
+  <si>
+    <t>The health care personnel category</t>
+  </si>
+  <si>
+    <t>Category of health care personnel authorization according to Helsepersonnelloven §48</t>
+  </si>
+  <si>
+    <t>urn:oid:2.16.578.1.12.4.1.1.9060</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding:healthPersonnellCategory.id</t>
+  </si>
+  <si>
     <t>Practitioner.qualification.code.coding.id</t>
   </si>
   <si>
+    <t>Practitioner.qualification.code.coding:healthPersonnellCategory.extension</t>
+  </si>
+  <si>
     <t>Practitioner.qualification.code.coding.extension</t>
   </si>
   <si>
+    <t>Practitioner.qualification.code.coding:healthPersonnellCategory.system</t>
+  </si>
+  <si>
     <t>Practitioner.qualification.code.coding.system</t>
   </si>
   <si>
-    <t>practitioner:authorization:system</t>
+    <t>Identification of the CodeSystem 9060 on Volven</t>
+  </si>
+  <si>
+    <t>Identification of the CodeSystem Kategori helsepersonell (OID=9060) used to describe the category of authorized health care personnel</t>
+  </si>
+  <si>
+    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
+  </si>
+  <si>
+    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
+  </si>
+  <si>
+    <t>Coding.system</t>
+  </si>
+  <si>
+    <t>C*E.3</t>
+  </si>
+  <si>
+    <t>./codeSystem</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding:healthPersonnellCategory.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding.version</t>
+  </si>
+  <si>
+    <t>Version of the system - if relevant</t>
+  </si>
+  <si>
+    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
+  </si>
+  <si>
+    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
+  </si>
+  <si>
+    <t>Coding.version</t>
+  </si>
+  <si>
+    <t>C*E.7</t>
+  </si>
+  <si>
+    <t>./codeSystemVersion</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding:healthPersonnellCategory.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding.code</t>
+  </si>
+  <si>
+    <t>Symbol in syntax defined by the system</t>
+  </si>
+  <si>
+    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
+  </si>
+  <si>
+    <t>Need to refer to a particular code in the system.</t>
+  </si>
+  <si>
+    <t>Coding.code</t>
+  </si>
+  <si>
+    <t>C*E.1</t>
+  </si>
+  <si>
+    <t>./code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding:healthPersonnellCategory.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
+  </si>
+  <si>
+    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
+  </si>
+  <si>
+    <t>Coding.display</t>
+  </si>
+  <si>
+    <t>C*E.2 - but note this is not well followed</t>
+  </si>
+  <si>
+    <t>CV.displayName</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding:healthPersonnellCategory.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding.userSelected</t>
+  </si>
+  <si>
+    <t>If this coding was chosen directly by the user</t>
+  </si>
+  <si>
+    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
+  </si>
+  <si>
+    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
+  </si>
+  <si>
+    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
+  </si>
+  <si>
+    <t>Coding.userSelected</t>
+  </si>
+  <si>
+    <t>Sometimes implied by being first</t>
+  </si>
+  <si>
+    <t>CD.codingRationale</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding:approvalType</t>
+  </si>
+  <si>
+    <t>approvalType</t>
+  </si>
+  <si>
+    <t>The approval type of the practitioner</t>
+  </si>
+  <si>
+    <t>The approval type of the practitioner (if applicable) according to the CodeSystem Godkjenningstype HPR (OID=7704)</t>
+  </si>
+  <si>
+    <t>urn:oid:2.16.578.1.12.4.1.1.7704</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding:approvalType.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding:approvalType.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding:approvalType.system</t>
+  </si>
+  <si>
+    <t>Identification of the CodeSystem 7704 on Volven</t>
+  </si>
+  <si>
+    <t>Identification of the CodeSystem Godkjenningstype HPR (OID=7704) used to describe type of autohorization registered in HPR.</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding:approvalType.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding:approvalType.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding:approvalType.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding:approvalType.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding:healthPersonnelSpecialization</t>
+  </si>
+  <si>
+    <t>healthPersonnelSpecialization</t>
+  </si>
+  <si>
+    <t>Godkjent spesialitet for helsepersonell registrert i HPR.</t>
+  </si>
+  <si>
+    <t>Godkjent spesialitet for helsepersonell registrert i HPR. Helsepersonellregisterets (HPR) klassifikasjon av spesialiteter (OID=7426)</t>
+  </si>
+  <si>
+    <t>urn:oid:2.16.578.1.12.4.1.1.7426</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding:healthPersonnelSpecialization.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding:healthPersonnelSpecialization.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding:healthPersonnelSpecialization.system</t>
+  </si>
+  <si>
+    <t>Identity of the terminology system</t>
   </si>
   <si>
     <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
   </si>
   <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.code.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.code.coding.code</t>
-  </si>
-  <si>
-    <t>practitioner:authorization:code</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.code.coding.display</t>
-  </si>
-  <si>
-    <t>practitioner:authorization:text</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification.code.coding.userSelected</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
+    <t>Practitioner.qualification.code.coding:healthPersonnelSpecialization.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding:healthPersonnelSpecialization.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding:healthPersonnelSpecialization.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification.code.coding:healthPersonnelSpecialization.userSelected</t>
   </si>
   <si>
     <t>Practitioner.qualification.code.text</t>
@@ -1757,12 +1833,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN61"/>
+  <dimension ref="A1:AN96"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="47.75" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="75.91015625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="47.75" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="28.5859375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -1770,7 +1846,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="23.58203125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="70.00390625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1795,9 +1871,9 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="56.17578125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="45.6171875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="52.3828125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="50.953125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -3022,16 +3098,14 @@
         <v>75</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC11" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="AF11" t="s" s="2">
         <v>143</v>
@@ -3049,24 +3123,24 @@
         <v>98</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3089,13 +3163,13 @@
         <v>75</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3146,7 +3220,7 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -3164,7 +3238,7 @@
         <v>75</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>75</v>
@@ -3175,10 +3249,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3207,7 +3281,7 @@
         <v>133</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N13" t="s" s="2">
         <v>135</v>
@@ -3248,19 +3322,19 @@
         <v>75</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
@@ -3278,7 +3352,7 @@
         <v>75</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>75</v>
@@ -3289,10 +3363,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3318,16 +3392,16 @@
         <v>106</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>75</v>
@@ -3352,13 +3426,13 @@
         <v>75</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>75</v>
@@ -3376,7 +3450,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -3394,7 +3468,7 @@
         <v>129</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>75</v>
@@ -3405,10 +3479,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3431,19 +3505,19 @@
         <v>87</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>75</v>
@@ -3468,13 +3542,13 @@
         <v>75</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>75</v>
@@ -3492,7 +3566,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -3507,10 +3581,10 @@
         <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>75</v>
@@ -3521,10 +3595,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3550,16 +3624,16 @@
         <v>100</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>75</v>
@@ -3572,7 +3646,7 @@
         <v>75</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>75</v>
@@ -3608,7 +3682,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
@@ -3623,13 +3697,13 @@
         <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>75</v>
@@ -3637,10 +3711,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3663,16 +3737,16 @@
         <v>87</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3686,7 +3760,7 @@
         <v>75</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>75</v>
@@ -3722,7 +3796,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -3737,13 +3811,13 @@
         <v>98</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>75</v>
@@ -3751,10 +3825,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3777,13 +3851,13 @@
         <v>87</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3834,7 +3908,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -3849,13 +3923,13 @@
         <v>98</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>75</v>
@@ -3863,10 +3937,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3889,16 +3963,16 @@
         <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3948,7 +4022,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -3963,13 +4037,13 @@
         <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>75</v>
@@ -3977,10 +4051,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4003,13 +4077,13 @@
         <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4060,7 +4134,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -4078,7 +4152,7 @@
         <v>75</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>75</v>
@@ -4089,10 +4163,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4121,7 +4195,7 @@
         <v>133</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>135</v>
@@ -4162,19 +4236,19 @@
         <v>75</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -4192,7 +4266,7 @@
         <v>75</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>75</v>
@@ -4203,10 +4277,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4229,16 +4303,16 @@
         <v>87</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4288,7 +4362,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -4297,7 +4371,7 @@
         <v>86</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>98</v>
@@ -4317,10 +4391,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4346,13 +4420,13 @@
         <v>100</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4378,13 +4452,13 @@
         <v>75</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>75</v>
@@ -4402,7 +4476,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -4431,10 +4505,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4460,13 +4534,13 @@
         <v>144</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4516,7 +4590,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>76</v>
@@ -4534,7 +4608,7 @@
         <v>75</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>75</v>
@@ -4545,10 +4619,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4571,16 +4645,16 @@
         <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4630,7 +4704,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4659,12 +4733,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>249</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>75</v>
       </c>
@@ -4673,7 +4749,7 @@
         <v>76</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>75</v>
@@ -4685,26 +4761,22 @@
         <v>87</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>248</v>
+        <v>144</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N26" t="s" s="2">
         <v>251</v>
       </c>
+      <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>252</v>
+        <v>147</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q26" t="s" s="2">
-        <v>253</v>
-      </c>
+      <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
         <v>75</v>
       </c>
@@ -4748,13 +4820,13 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>247</v>
+        <v>143</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>75</v>
@@ -4763,24 +4835,24 @@
         <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>254</v>
+        <v>151</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>255</v>
+        <v>153</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>256</v>
+        <v>154</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4791,7 +4863,7 @@
         <v>76</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>75</v>
@@ -4800,23 +4872,19 @@
         <v>75</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>257</v>
+        <v>155</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>258</v>
+        <v>156</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>75</v>
       </c>
@@ -4864,28 +4932,28 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>256</v>
+        <v>158</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>262</v>
+        <v>75</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>263</v>
+        <v>159</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>264</v>
+        <v>75</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>75</v>
@@ -4893,21 +4961,21 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>265</v>
+        <v>160</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>75</v>
@@ -4919,15 +4987,17 @@
         <v>75</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>135</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>75</v>
@@ -4964,37 +5034,37 @@
         <v>75</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>75</v>
+        <v>162</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>75</v>
+        <v>163</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>75</v>
+        <v>137</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>75</v>
@@ -5005,44 +5075,46 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>266</v>
+        <v>165</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>169</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>75</v>
       </c>
@@ -5066,49 +5138,49 @@
         <v>75</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>75</v>
+        <v>171</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>75</v>
+        <v>172</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>161</v>
+        <v>75</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>162</v>
+        <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>75</v>
@@ -5119,10 +5191,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>267</v>
+        <v>175</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5139,25 +5211,25 @@
         <v>75</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="J30" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>106</v>
+        <v>176</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>268</v>
+        <v>177</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>269</v>
+        <v>178</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>270</v>
+        <v>179</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>271</v>
+        <v>180</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>75</v>
@@ -5182,13 +5254,13 @@
         <v>75</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>272</v>
+        <v>182</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>273</v>
+        <v>183</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>75</v>
@@ -5206,7 +5278,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>274</v>
+        <v>184</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -5221,13 +5293,13 @@
         <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>275</v>
+        <v>185</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>276</v>
+        <v>174</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>277</v>
+        <v>75</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>75</v>
@@ -5235,10 +5307,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>278</v>
+        <v>256</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>278</v>
+        <v>186</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5246,7 +5318,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>86</v>
@@ -5261,32 +5333,32 @@
         <v>87</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>153</v>
+        <v>100</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>279</v>
+        <v>257</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>280</v>
+        <v>257</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>281</v>
+        <v>189</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>282</v>
+        <v>190</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>75</v>
+        <v>258</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="T31" t="s" s="2">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="U31" t="s" s="2">
         <v>75</v>
@@ -5322,7 +5394,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>283</v>
+        <v>192</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -5337,13 +5409,13 @@
         <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>284</v>
+        <v>193</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>285</v>
+        <v>194</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>75</v>
+        <v>195</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>75</v>
@@ -5351,18 +5423,18 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>286</v>
+        <v>259</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>286</v>
+        <v>196</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>287</v>
+        <v>75</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>86</v>
@@ -5377,16 +5449,16 @@
         <v>87</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>288</v>
+        <v>260</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>290</v>
+        <v>199</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5400,7 +5472,7 @@
         <v>75</v>
       </c>
       <c r="T32" t="s" s="2">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="U32" t="s" s="2">
         <v>75</v>
@@ -5436,7 +5508,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>291</v>
+        <v>201</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5451,13 +5523,13 @@
         <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>292</v>
+        <v>202</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>293</v>
+        <v>203</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>294</v>
+        <v>204</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>75</v>
@@ -5465,21 +5537,21 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>295</v>
+        <v>261</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>295</v>
+        <v>205</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>296</v>
+        <v>75</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>75</v>
@@ -5491,17 +5563,15 @@
         <v>87</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>153</v>
+        <v>206</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>297</v>
+        <v>207</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>299</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>75</v>
@@ -5550,13 +5620,13 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>300</v>
+        <v>209</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>75</v>
@@ -5565,13 +5635,13 @@
         <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>301</v>
+        <v>210</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>302</v>
+        <v>211</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>303</v>
+        <v>212</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>75</v>
@@ -5579,10 +5649,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>304</v>
+        <v>262</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>304</v>
+        <v>213</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5593,7 +5663,7 @@
         <v>76</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>75</v>
@@ -5605,15 +5675,17 @@
         <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>153</v>
+        <v>214</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>305</v>
+        <v>215</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>75</v>
@@ -5662,13 +5734,13 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>307</v>
+        <v>218</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>75</v>
@@ -5677,13 +5749,13 @@
         <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>308</v>
+        <v>219</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>309</v>
+        <v>220</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>310</v>
+        <v>221</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>75</v>
@@ -5691,12 +5763,14 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>311</v>
+        <v>263</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="C35" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>264</v>
+      </c>
       <c r="D35" t="s" s="2">
         <v>75</v>
       </c>
@@ -5717,16 +5791,18 @@
         <v>87</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>312</v>
+        <v>265</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>313</v>
+        <v>266</v>
       </c>
       <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>75</v>
       </c>
@@ -5774,7 +5850,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>314</v>
+        <v>143</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5789,24 +5865,24 @@
         <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>315</v>
+        <v>150</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>316</v>
+        <v>151</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>75</v>
+        <v>153</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>317</v>
+        <v>267</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>317</v>
+        <v>154</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5826,21 +5902,19 @@
         <v>75</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>205</v>
+        <v>155</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>318</v>
+        <v>156</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>319</v>
+        <v>157</v>
       </c>
       <c r="N36" s="2"/>
-      <c r="O36" t="s" s="2">
-        <v>320</v>
-      </c>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>75</v>
       </c>
@@ -5888,7 +5962,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>321</v>
+        <v>158</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5900,16 +5974,16 @@
         <v>75</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>98</v>
+        <v>75</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>322</v>
+        <v>75</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>323</v>
+        <v>159</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>211</v>
+        <v>75</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>75</v>
@@ -5917,14 +5991,14 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>324</v>
+        <v>268</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>324</v>
+        <v>160</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5940,23 +6014,21 @@
         <v>75</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>325</v>
+        <v>132</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>326</v>
+        <v>133</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>327</v>
+        <v>161</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>135</v>
+      </c>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>75</v>
       </c>
@@ -5992,19 +6064,19 @@
         <v>75</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>75</v>
+        <v>162</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>75</v>
+        <v>163</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>324</v>
+        <v>164</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -6016,16 +6088,16 @@
         <v>75</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>330</v>
+        <v>75</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>331</v>
+        <v>159</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>332</v>
+        <v>75</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>75</v>
@@ -6033,10 +6105,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>333</v>
+        <v>269</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>333</v>
+        <v>165</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6047,31 +6119,31 @@
         <v>76</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>87</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>334</v>
+        <v>106</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>335</v>
+        <v>166</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>336</v>
+        <v>167</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>337</v>
+        <v>168</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>338</v>
+        <v>169</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>75</v>
@@ -6096,13 +6168,13 @@
         <v>75</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>75</v>
+        <v>171</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>75</v>
+        <v>172</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>75</v>
@@ -6120,13 +6192,13 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>333</v>
+        <v>173</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>75</v>
@@ -6135,13 +6207,13 @@
         <v>98</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>339</v>
+        <v>129</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>340</v>
+        <v>174</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>341</v>
+        <v>75</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>75</v>
@@ -6149,10 +6221,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>342</v>
+        <v>270</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>342</v>
+        <v>175</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6175,17 +6247,19 @@
         <v>87</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>106</v>
+        <v>176</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>343</v>
+        <v>177</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O39" t="s" s="2">
-        <v>345</v>
+        <v>180</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>75</v>
@@ -6210,13 +6284,13 @@
         <v>75</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>346</v>
+        <v>182</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>347</v>
+        <v>183</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>75</v>
@@ -6234,7 +6308,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>342</v>
+        <v>184</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -6249,13 +6323,13 @@
         <v>98</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>348</v>
+        <v>185</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>349</v>
+        <v>174</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>350</v>
+        <v>75</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>75</v>
@@ -6263,10 +6337,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>351</v>
+        <v>271</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>351</v>
+        <v>186</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6274,7 +6348,7 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>86</v>
@@ -6289,30 +6363,32 @@
         <v>87</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>352</v>
+        <v>100</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>353</v>
+        <v>272</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>189</v>
+      </c>
       <c r="O40" t="s" s="2">
-        <v>355</v>
+        <v>190</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" t="s" s="2">
-        <v>75</v>
+        <v>273</v>
       </c>
       <c r="S40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>75</v>
@@ -6348,7 +6424,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>351</v>
+        <v>192</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -6363,13 +6439,13 @@
         <v>98</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>356</v>
+        <v>193</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>357</v>
+        <v>194</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>358</v>
+        <v>195</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>75</v>
@@ -6377,10 +6453,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>359</v>
+        <v>274</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>359</v>
+        <v>196</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6388,10 +6464,10 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>75</v>
@@ -6400,21 +6476,21 @@
         <v>75</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>360</v>
+        <v>155</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>361</v>
+        <v>275</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" t="s" s="2">
-        <v>363</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>75</v>
       </c>
@@ -6426,7 +6502,7 @@
         <v>75</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>75</v>
@@ -6462,13 +6538,13 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>359</v>
+        <v>201</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>75</v>
@@ -6477,13 +6553,13 @@
         <v>98</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>75</v>
+        <v>202</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>364</v>
+        <v>203</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>365</v>
+        <v>204</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>75</v>
@@ -6491,10 +6567,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>366</v>
+        <v>276</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>366</v>
+        <v>205</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6505,7 +6581,7 @@
         <v>76</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>75</v>
@@ -6514,16 +6590,16 @@
         <v>75</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>367</v>
+        <v>206</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>368</v>
+        <v>207</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>369</v>
+        <v>208</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6574,13 +6650,13 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>366</v>
+        <v>209</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>75</v>
@@ -6589,13 +6665,13 @@
         <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>370</v>
+        <v>210</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>371</v>
+        <v>211</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>372</v>
+        <v>212</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>75</v>
@@ -6603,10 +6679,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>373</v>
+        <v>277</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>373</v>
+        <v>213</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6626,18 +6702,20 @@
         <v>75</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>153</v>
+        <v>214</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>154</v>
+        <v>215</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N43" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>75</v>
@@ -6686,7 +6764,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>156</v>
+        <v>218</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -6698,16 +6776,16 @@
         <v>75</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>75</v>
+        <v>219</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>157</v>
+        <v>220</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>75</v>
+        <v>221</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>75</v>
@@ -6715,14 +6793,16 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>374</v>
+        <v>278</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>143</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="D44" t="s" s="2">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6738,21 +6818,21 @@
         <v>75</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>133</v>
+        <v>280</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O44" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" t="s" s="2">
+        <v>147</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>75</v>
       </c>
@@ -6800,7 +6880,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6812,63 +6892,59 @@
         <v>75</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>75</v>
+        <v>153</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>375</v>
+        <v>282</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>375</v>
+        <v>154</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>376</v>
+        <v>75</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I45" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>132</v>
+        <v>155</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>377</v>
+        <v>156</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>141</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>75</v>
       </c>
@@ -6916,25 +6992,25 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>379</v>
+        <v>158</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>75</v>
@@ -6945,14 +7021,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>380</v>
+        <v>283</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>380</v>
+        <v>160</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>75</v>
+        <v>131</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6971,18 +7047,18 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>381</v>
+        <v>133</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>383</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>75</v>
       </c>
@@ -7018,19 +7094,19 @@
         <v>75</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>75</v>
+        <v>162</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>75</v>
+        <v>163</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>380</v>
+        <v>164</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -7042,13 +7118,13 @@
         <v>75</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>384</v>
+        <v>159</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>75</v>
@@ -7059,10 +7135,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>385</v>
+        <v>284</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>385</v>
+        <v>165</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7070,7 +7146,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>86</v>
@@ -7079,22 +7155,26 @@
         <v>75</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>175</v>
+        <v>106</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>386</v>
+        <v>166</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>167</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>169</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>75</v>
       </c>
@@ -7118,13 +7198,13 @@
         <v>75</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>388</v>
+        <v>170</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>389</v>
+        <v>171</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>390</v>
+        <v>172</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>75</v>
@@ -7142,10 +7222,10 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>385</v>
+        <v>173</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="AH47" t="s" s="2">
         <v>86</v>
@@ -7157,13 +7237,13 @@
         <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>75</v>
+        <v>129</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>371</v>
+        <v>174</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>391</v>
+        <v>75</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>75</v>
@@ -7171,10 +7251,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>392</v>
+        <v>285</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>392</v>
+        <v>175</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7194,19 +7274,23 @@
         <v>75</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>154</v>
+        <v>177</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>180</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>75</v>
       </c>
@@ -7230,13 +7314,13 @@
         <v>75</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>75</v>
+        <v>181</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>75</v>
+        <v>182</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>75</v>
+        <v>183</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>75</v>
@@ -7254,7 +7338,7 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>156</v>
+        <v>184</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -7266,13 +7350,13 @@
         <v>75</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>75</v>
+        <v>185</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>75</v>
@@ -7283,21 +7367,21 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>393</v>
+        <v>286</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>393</v>
+        <v>186</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>75</v>
@@ -7306,33 +7390,35 @@
         <v>75</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>132</v>
+        <v>100</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>133</v>
+        <v>287</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>159</v>
+        <v>288</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>135</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>189</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>75</v>
+        <v>289</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>75</v>
+        <v>191</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>75</v>
@@ -7356,40 +7442,40 @@
         <v>75</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>161</v>
+        <v>75</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>162</v>
+        <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>163</v>
+        <v>192</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>75</v>
+        <v>193</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>157</v>
+        <v>194</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>75</v>
+        <v>195</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>75</v>
@@ -7397,10 +7483,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>394</v>
+        <v>290</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>394</v>
+        <v>196</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7408,10 +7494,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>75</v>
@@ -7423,20 +7509,18 @@
         <v>87</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>395</v>
+        <v>155</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>396</v>
+        <v>291</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>397</v>
+        <v>292</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>75</v>
       </c>
@@ -7448,7 +7532,7 @@
         <v>75</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>75</v>
@@ -7484,13 +7568,13 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>400</v>
+        <v>201</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>75</v>
@@ -7499,13 +7583,13 @@
         <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>401</v>
+        <v>202</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>402</v>
+        <v>203</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>75</v>
+        <v>204</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>75</v>
@@ -7513,10 +7597,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>403</v>
+        <v>293</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>403</v>
+        <v>205</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7536,16 +7620,16 @@
         <v>75</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>153</v>
+        <v>206</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>154</v>
+        <v>207</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>155</v>
+        <v>208</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7596,7 +7680,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>156</v>
+        <v>209</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -7608,16 +7692,16 @@
         <v>75</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>75</v>
+        <v>210</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>157</v>
+        <v>211</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>75</v>
+        <v>212</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>75</v>
@@ -7625,21 +7709,21 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>404</v>
+        <v>294</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>404</v>
+        <v>213</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>131</v>
+        <v>75</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>75</v>
@@ -7648,19 +7732,19 @@
         <v>75</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>132</v>
+        <v>214</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>133</v>
+        <v>215</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>159</v>
+        <v>216</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>135</v>
+        <v>217</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7698,40 +7782,40 @@
         <v>75</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>161</v>
+        <v>75</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>162</v>
+        <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>163</v>
+        <v>218</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>75</v>
+        <v>219</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>157</v>
+        <v>220</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>75</v>
+        <v>221</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>75</v>
@@ -7739,10 +7823,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>405</v>
+        <v>295</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>405</v>
+        <v>295</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7765,24 +7849,26 @@
         <v>87</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>100</v>
+        <v>296</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>406</v>
+        <v>297</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>407</v>
+        <v>298</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>408</v>
+        <v>299</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>409</v>
+        <v>300</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q53" s="2"/>
+      <c r="Q53" t="s" s="2">
+        <v>301</v>
+      </c>
       <c r="R53" t="s" s="2">
         <v>75</v>
       </c>
@@ -7826,7 +7912,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>410</v>
+        <v>295</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7841,24 +7927,24 @@
         <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>411</v>
+        <v>75</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>412</v>
+        <v>302</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>75</v>
+        <v>303</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>413</v>
+        <v>304</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>413</v>
+        <v>304</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7869,7 +7955,7 @@
         <v>76</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>75</v>
@@ -7878,21 +7964,23 @@
         <v>75</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>153</v>
+        <v>305</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>414</v>
+        <v>306</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>415</v>
+        <v>307</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>75</v>
       </c>
@@ -7940,28 +8028,28 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>417</v>
+        <v>304</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>75</v>
+        <v>310</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>418</v>
+        <v>311</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>419</v>
+        <v>312</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>75</v>
+        <v>313</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>75</v>
@@ -7969,10 +8057,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>420</v>
+        <v>314</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>420</v>
+        <v>314</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7983,7 +8071,7 @@
         <v>76</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>75</v>
@@ -7995,17 +8083,19 @@
         <v>87</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>106</v>
+        <v>315</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>421</v>
+        <v>316</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="O55" t="s" s="2">
-        <v>423</v>
+        <v>319</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>75</v>
@@ -8054,13 +8144,13 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>424</v>
+        <v>314</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>75</v>
@@ -8069,13 +8159,13 @@
         <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>425</v>
+        <v>320</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>426</v>
+        <v>321</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>75</v>
+        <v>322</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>75</v>
@@ -8083,10 +8173,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>427</v>
+        <v>323</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>427</v>
+        <v>323</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8097,7 +8187,7 @@
         <v>76</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>75</v>
@@ -8106,20 +8196,22 @@
         <v>75</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>153</v>
+        <v>324</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>428</v>
+        <v>325</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="O56" t="s" s="2">
-        <v>430</v>
+        <v>328</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>75</v>
@@ -8168,28 +8260,28 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>431</v>
+        <v>323</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>75</v>
+        <v>310</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>98</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>432</v>
+        <v>329</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>433</v>
+        <v>330</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>75</v>
+        <v>331</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>75</v>
@@ -8197,10 +8289,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>434</v>
+        <v>332</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>434</v>
+        <v>332</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8223,19 +8315,17 @@
         <v>87</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>248</v>
+        <v>106</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>435</v>
+        <v>333</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>437</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>438</v>
+        <v>335</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>75</v>
@@ -8260,13 +8350,13 @@
         <v>75</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>75</v>
+        <v>336</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>75</v>
+        <v>337</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>75</v>
@@ -8284,7 +8374,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>439</v>
+        <v>332</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -8299,13 +8389,13 @@
         <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>440</v>
+        <v>338</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>441</v>
+        <v>339</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>75</v>
+        <v>340</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>75</v>
@@ -8313,10 +8403,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>442</v>
+        <v>341</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>442</v>
+        <v>341</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8339,19 +8429,17 @@
         <v>87</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>153</v>
+        <v>342</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>443</v>
+        <v>343</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>445</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>446</v>
+        <v>345</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>75</v>
@@ -8400,7 +8488,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>447</v>
+        <v>341</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>76</v>
@@ -8415,13 +8503,13 @@
         <v>98</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>448</v>
+        <v>346</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>449</v>
+        <v>347</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>75</v>
+        <v>348</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>75</v>
@@ -8429,10 +8517,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>450</v>
+        <v>349</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>450</v>
+        <v>349</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8443,7 +8531,7 @@
         <v>76</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>75</v>
@@ -8455,17 +8543,17 @@
         <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>205</v>
+        <v>350</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>451</v>
+        <v>351</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>452</v>
+        <v>352</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>453</v>
+        <v>353</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>75</v>
@@ -8514,13 +8602,13 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>450</v>
+        <v>349</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>75</v>
@@ -8532,10 +8620,10 @@
         <v>75</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>454</v>
+        <v>354</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>455</v>
+        <v>355</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>75</v>
@@ -8543,10 +8631,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>456</v>
+        <v>356</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>456</v>
+        <v>356</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8557,7 +8645,7 @@
         <v>76</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>75</v>
@@ -8569,13 +8657,13 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>213</v>
+        <v>357</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>457</v>
+        <v>358</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>458</v>
+        <v>359</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8626,13 +8714,13 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>456</v>
+        <v>356</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>75</v>
@@ -8641,13 +8729,13 @@
         <v>98</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>75</v>
+        <v>360</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>459</v>
+        <v>361</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>75</v>
+        <v>362</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>75</v>
@@ -8655,10 +8743,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>460</v>
+        <v>363</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>460</v>
+        <v>363</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8669,7 +8757,7 @@
         <v>76</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>75</v>
@@ -8681,20 +8769,16 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>461</v>
+        <v>156</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>464</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>75</v>
       </c>
@@ -8718,54 +8802,4056 @@
         <v>75</v>
       </c>
       <c r="X61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN61" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="C62" s="2"/>
+      <c r="D62" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="E62" s="2"/>
+      <c r="F62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K62" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L62" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M62" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O62" s="2"/>
+      <c r="P62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF62" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG62" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ62" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AK62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL62" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN62" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="C63" s="2"/>
+      <c r="D63" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="E63" s="2"/>
+      <c r="F63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I63" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="J63" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K63" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L63" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF63" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="AG63" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ63" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AK63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="N64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="P64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="AC68" s="2"/>
+      <c r="AD68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="C69" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="D69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="P69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X69" t="s" s="2">
         <v>110</v>
       </c>
-      <c r="Y61" t="s" s="2">
+      <c r="Y69" s="2"/>
+      <c r="Z69" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="O73" s="2"/>
+      <c r="P73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN73" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="P75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="P76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="C77" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="D77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="Y77" s="2"/>
+      <c r="Z77" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O79" s="2"/>
+      <c r="P79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="P80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="P82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="P83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="P84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="C85" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="D85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="P85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="Y85" s="2"/>
+      <c r="Z85" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="O89" s="2"/>
+      <c r="P89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="P90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="P91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="O92" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="P92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="P93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="N94" s="2"/>
+      <c r="O94" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="P94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="P96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="Y96" t="s" s="2">
         <v>111</v>
       </c>
-      <c r="Z61" t="s" s="2">
+      <c r="Z96" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="AA61" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH61" t="s" s="2">
+      <c r="AA96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH96" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="AI61" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
+      <c r="AI96" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
         <v>98</v>
       </c>
-      <c r="AK61" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="AN61" t="s" s="2">
+      <c r="AK96" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AN96" t="s" s="2">
         <v>75</v>
       </c>
     </row>
